--- a/data-raw/TA 616 Treatment Admin and monitoring costs .xlsx
+++ b/data-raw/TA 616 Treatment Admin and monitoring costs .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob.sharepoint.com/teams/grp-Bristol_TAG-MTA-MS/Shared Documents/MTA-MS/Working Folder_HE/MS Models/Git Repo/MS-MTA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_1CAB97146400357675ADF1393DF30195AC93AD3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{875239F2-1CFE-4F04-A089-288FC91B92EF}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_1CAB97146400357675ADF1393DF30195AC93AD3B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{069BD220-8412-451A-A70E-0ADE853C64BD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="495" windowWidth="19545" windowHeight="15105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="page 70" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <r>
       <rPr>
@@ -694,78 +694,12 @@
     <t>Admin costs</t>
   </si>
   <si>
-    <t>Monitoring costs</t>
-  </si>
-  <si>
     <t>Year 1</t>
   </si>
   <si>
     <t>Year 2+</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cladribine:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">RES·
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>RRMS</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>patients</t>
-    </r>
-  </si>
-  <si>
     <t>£25,917</t>
   </si>
   <si>
@@ -780,120 +714,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>£584</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>£215</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cladribine:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>RRMS</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>patients</t>
-    </r>
-  </si>
-  <si>
     <t>£26,373</t>
   </si>
   <si>
@@ -909,12 +729,6 @@
     <t>£1,681</t>
   </si>
   <si>
-    <t>£444</t>
-  </si>
-  <si>
-    <t>£267</t>
-  </si>
-  <si>
     <t>Daclizumab</t>
   </si>
   <si>
@@ -927,12 +741,6 @@
     <t>£0</t>
   </si>
   <si>
-    <t>£349</t>
-  </si>
-  <si>
-    <t>£187</t>
-  </si>
-  <si>
     <t>Fingolimod</t>
   </si>
   <si>
@@ -942,12 +750,6 @@
     <t>£551</t>
   </si>
   <si>
-    <t>£821</t>
-  </si>
-  <si>
-    <t>£169</t>
-  </si>
-  <si>
     <t>Natalizumab</t>
   </si>
   <si>
@@ -957,12 +759,6 @@
     <t>£7,159</t>
   </si>
   <si>
-    <t>£540</t>
-  </si>
-  <si>
-    <t>£547</t>
-  </si>
-  <si>
     <t>Relapse costs</t>
   </si>
   <si>
@@ -970,6 +766,21 @@
   </si>
   <si>
     <t>Without hospitalisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costs_monitoring </t>
+  </si>
+  <si>
+    <t>costs_monitoring_year1</t>
+  </si>
+  <si>
+    <t>costs_monitoring_year2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladribine SOT RRMS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cladribine RES RRMS </t>
   </si>
 </sst>
 </file>
@@ -1048,7 +859,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1099,17 +910,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
@@ -1216,55 +1016,76 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1274,12 +1095,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1287,24 +1102,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1620,233 +1417,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="408.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="233.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="24"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
+      <c r="A4" s="22" t="s">
+        <v>1</v>
+      </c>
       <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="59.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="F5" s="4">
+        <v>584</v>
+      </c>
+      <c r="G5" s="5">
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="58.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="27"/>
+        <v>29</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="18"/>
       <c r="D6" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="F6" s="7">
+        <v>584</v>
+      </c>
+      <c r="G6" s="8">
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="17"/>
       <c r="D7" s="9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="F7" s="9">
+        <v>444</v>
+      </c>
+      <c r="G7" s="10">
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="27"/>
+        <v>13</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="18"/>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="F8" s="1">
+        <v>349</v>
+      </c>
+      <c r="G8" s="2">
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="26"/>
+        <v>17</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="17"/>
       <c r="D9" s="9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="F9" s="9">
+        <v>821</v>
+      </c>
+      <c r="G9" s="10">
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="28"/>
+        <v>20</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="19"/>
       <c r="D10" s="14" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>35</v>
+        <v>22</v>
+      </c>
+      <c r="F10" s="14">
+        <v>540</v>
+      </c>
+      <c r="G10" s="15">
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
+      <c r="A11" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:8" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="29">
+        <v>24</v>
+      </c>
+      <c r="B12" s="20">
         <v>3463</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="29">
+        <v>25</v>
+      </c>
+      <c r="B13" s="20">
         <v>526</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
